--- a/data/outputs/feature_dictionary.xlsx
+++ b/data/outputs/feature_dictionary.xlsx
@@ -413,1545 +413,3594 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Feature Name</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Data Type</t>
+          <t>column</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Sample Value</t>
+          <t>dtype</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Feature Category</t>
+          <t>pct_non_null</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Suitable for ML?</t>
+          <t>is_feature</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>row_id</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8865050ae7fffff</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Key ID</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Key ID</t>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42.196657159607796</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>datetime64[us]</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dl_mean</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>dl_median</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44.30649001758819</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Median download throughput (Mbps) for this cell-hour.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dl_std</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>dl_mean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.329498573941169</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dl_p95</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>dl_std</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.855654307490134</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ul_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>dl_p95</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15.087069272941878</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ul_mean</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>ul_median</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15.841422736588973</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ul_std</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>ul_mean</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.263060390941282</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>ul_std</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35.23382519050346</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rtt_mean</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rtt_median</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>36.99551645002863</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Median round-trip latency (ms) for this cell-hour.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rtt_std</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rtt_mean</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.046765038100692</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jitter_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rtt_std</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8.569794894508718</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>loss_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>jitter_median</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.14429932505533294</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>test_sample_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>loss_median</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>unique_device_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>test_sample_count</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pop_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>unique_device_count</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>qoe_is_synthetic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>True if this cell-hour's QoE values are model-generated rather than Ookla-anchored.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>hour_of_day</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>36990.5485</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>day_of_week</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.05016844425878884</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>is_weekend</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>is_peak_period</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>lag_1h_dl_median</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Value of dl_median exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>lag_2h_dl_median</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>lag_24h_dl_median</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Value of dl_median exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>road_length_expressway_m</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rolling_mean_24h_dl_median</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2843.2405535249677</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>road_length_primary_m</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rolling_std_24h_dl_median</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>283.43264422092227</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tower_count_res8</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>lag_1h_dl_median_valid</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Value of dl_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>lag_2h_dl_median_valid</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>70.21115050482373</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dominant_landcover_class</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>lag_24h_dl_median_valid</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Spatial/Demographic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Value of dl_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>spatial_lag_dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rolling_mean_24h_dl_median_valid</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>40.911683192074136</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>spatial_lag_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>lag_1h_rtt_median</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>29.897141364470322</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Value of rtt_median exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>spatial_lag_pop_count</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>lag_2h_rtt_median</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2212.6666666666665</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hour_of_day</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>lag_24h_rtt_median</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Value of rtt_median exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>day_of_week</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>rolling_mean_24h_rtt_median</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>is_weekend</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>rolling_std_24h_rtt_median</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>is_peak_period</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>lag_1h_rtt_median_valid</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Value of rtt_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lag_1h_dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>lag_2h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>42.196657159607796</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>lag_2h_dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>lag_24h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>42.196657159607796</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Value of rtt_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>lag_24h_dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>rolling_mean_24h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>42.196657159607796</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>qoe_trend_1h</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>42.196657159607796</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rolling_std_24h_dl_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>in_warmup_window</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lag_1h_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>35.23382519050346</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>lag_2h_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>35.23382519050346</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>lag_24h_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>35.23382519050346</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>35.23382519050346</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rolling_std_24h_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qoe_trend_1h</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>demand_pressure_index</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>18.670437379739344</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>spatial_lag_demand_pressure_index</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>24.85017354429698</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>getis_ord_gi_zscore_rtt_median</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-0.4132157205669514</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>target_qoe_score</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>62.878155738487045</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Target Variable</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>No (Target)</t>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>target_mos</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.5151262295394816</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Target Variable</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>No (Target)</t>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>poi_healthcare_count</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Target Variable</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>No (Target)</t>
+      <c r="D55" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>poi_retail_food_count</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>int64</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Target Variable</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>No (Target)</t>
+      <c r="D56" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>poi_office_count</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>poi_recreation_count</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>road_length_m</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>road_density_km_per_km2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>intersection_count</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>intersection_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>100</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>dist_to_nearest_transit_m</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>100</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>poi_transport_stop_count</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>100</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>osm_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>population_night</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>WorldPop-derived residential population estimate for the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>population_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>100</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>population_day</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>population_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>100</v>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>demand_pressure_base</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>demand_pressure_index_pre_spatial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>100</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>spatial_lag_dl_median</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>spatial_var_dl_median</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>100</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>spatial_lag_rtt_median</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>spatial_var_rtt_median</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>spatial_lag_population_night</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>100</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>spatial_var_population_night</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>100</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>100</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>spatial_var_demand_pressure_index_pre_spatial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>100</v>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>demand_pressure_index</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>100</v>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0-100 composite demand pressure (population, POI, built-up, roads, historical QoE, nearby demand).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>spatial_rolling_mean_24h_dl_median</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>100</v>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>gi_star_zscore_rtt_median</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>100</v>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Getis-Ord Gi* z-score for latency (esda.G_Local, star=True).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>gi_star_pvalue_rtt_median</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>float32</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>100</v>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>hotspot_category_rtt_median</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>100</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Hot/cold spot classification at 90/95/99% confidence (esda.G_Local p-values).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>local_moran_i_rtt_median</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>100</v>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>local_moran_pvalue_rtt_median</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>100</v>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>local_moran_quadrant_rtt_median</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>100</v>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>HH/LH/LL/HL spatial cluster/outlier classification (esda.Moran_Local).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>historical_hotspot_freq_rtt_median</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>100</v>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real hotspot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>target_qoe_score</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>100</v>
+      </c>
+      <c r="E89" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Composite 0-100 QoE score (ITU-inspired).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>target_mos</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>100</v>
+      </c>
+      <c r="E90" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mean Opinion Score estimate (1.0-5.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>target_is_degraded</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>100</v>
+      </c>
+      <c r="E91" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Binary degradation flag (dl below threshold OR rtt above threshold).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>target_degradation_class</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>100</v>
+      </c>
+      <c r="E92" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0=normal, 1=degraded, 2=severe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cell_time_dataset</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>qoe_confidence_score</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>float64</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Dynamic/Lag</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>100</v>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>h3_index</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>100</v>
+      </c>
+      <c r="E94" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>tower_count</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>tower_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>100</v>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dist_to_nearest_tower_m</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>100</v>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>tower_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>100</v>
+      </c>
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>building_count</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>100</v>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>total_building_area_m2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>built_up_ratio</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>100</v>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>building_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>100</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>avg_building_footprint_m2</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>100</v>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>building_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>100</v>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>poi_education_count</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>100</v>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>poi_healthcare_count</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>100</v>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>poi_retail_food_count</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>100</v>
+      </c>
+      <c r="E107" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>poi_office_count</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>100</v>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>poi_recreation_count</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>100</v>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>road_length_m</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>100</v>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>road_density_km_per_km2</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>100</v>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>intersection_count</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>100</v>
+      </c>
+      <c r="E112" t="b">
+        <v>1</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>intersection_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>100</v>
+      </c>
+      <c r="E113" t="b">
+        <v>1</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>dist_to_nearest_transit_m</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>100</v>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>poi_transport_stop_count</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>100</v>
+      </c>
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>osm_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>100</v>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>population_night</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>100</v>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>WorldPop-derived residential population estimate for the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>population_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>100</v>
+      </c>
+      <c r="E118" t="b">
+        <v>1</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>population_day</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>100</v>
+      </c>
+      <c r="E119" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>population_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>100</v>
+      </c>
+      <c r="E120" t="b">
+        <v>1</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>100</v>
+      </c>
+      <c r="E121" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>h3_index</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>100</v>
+      </c>
+      <c r="E122" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>datetime64[us]</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>100</v>
+      </c>
+      <c r="E123" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>target_qoe_score</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>100</v>
+      </c>
+      <c r="E124" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Composite 0-100 QoE score (ITU-inspired).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>target_mos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>100</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mean Opinion Score estimate (1.0-5.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>target_is_degraded</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>100</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Binary degradation flag (dl below threshold OR rtt above threshold).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>target_degradation_class</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>100</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0=normal, 1=degraded, 2=severe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>qoe_confidence_score</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>100</v>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>See src/data_preprocessing/ module docstrings.</t>
         </is>
       </c>
     </row>

--- a/data/outputs/feature_dictionary.xlsx
+++ b/data/outputs/feature_dictionary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,10 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>is_feature</t>
+          <t>is_feature_for_current_target</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>is_feature_for_next_hour_target</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>leakage_risk_note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -470,7 +480,11 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
         </is>
@@ -498,7 +512,11 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
@@ -526,7 +544,11 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
         </is>
@@ -554,9 +576,13 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Median download throughput (Mbps) for this cell-hour.</t>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Median simulated download throughput (Mbps) for this cell-hour. NOT a measurement — see config.SIMULATION_DISCLAIMER.</t>
         </is>
       </c>
     </row>
@@ -582,9 +608,13 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>dl_median x 1.05 (formula-derived, not an independent statistic). Excluded from features when predicting the SAME-HOUR target (leakage); allowed for next-hour prediction.</t>
         </is>
       </c>
     </row>
@@ -610,9 +640,13 @@
       <c r="E7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>dl_median x 0.15 (formula-derived). Same leakage caveat as dl_mean.</t>
         </is>
       </c>
     </row>
@@ -638,9 +672,13 @@
       <c r="E8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>dl_median x 1.30 (formula-derived). Same leakage caveat as dl_mean.</t>
         </is>
       </c>
     </row>
@@ -666,9 +704,13 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Median simulated upload throughput (Mbps) for this cell-hour. Simulated, see above.</t>
         </is>
       </c>
     </row>
@@ -694,9 +736,13 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ul_median x 1.05 (formula-derived).</t>
         </is>
       </c>
     </row>
@@ -722,9 +768,13 @@
       <c r="E11" t="b">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ul_median x 0.15 (formula-derived).</t>
         </is>
       </c>
     </row>
@@ -750,9 +800,13 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Median round-trip latency (ms) for this cell-hour.</t>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Median simulated round-trip latency (ms) for this cell-hour. Simulated, see above.</t>
         </is>
       </c>
     </row>
@@ -778,9 +832,13 @@
       <c r="E13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>rtt_median x 1.05 (formula-derived).</t>
         </is>
       </c>
     </row>
@@ -806,9 +864,13 @@
       <c r="E14" t="b">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>rtt_median x 0.20 (formula-derived).</t>
         </is>
       </c>
     </row>
@@ -834,9 +896,13 @@
       <c r="E15" t="b">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Simulated jitter (ms), derived from rtt_median plus noise.</t>
         </is>
       </c>
     </row>
@@ -862,9 +928,13 @@
       <c r="E16" t="b">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Simulated packet loss percentage, derived from the same load_factor as dl/rtt.</t>
         </is>
       </c>
     </row>
@@ -890,9 +960,13 @@
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Real Ookla test count where a real anchor exists for the cell; Poisson-simulated otherwise. Represents measurement VOLUME, not the outcome — safe as a feature in either target mode.</t>
         </is>
       </c>
     </row>
@@ -918,9 +992,13 @@
       <c r="E18" t="b">
         <v>1</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>~70% of test_sample_count (rounded). Same status as test_sample_count.</t>
         </is>
       </c>
     </row>
@@ -932,7 +1010,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qoe_is_synthetic</t>
+          <t>qoe_level_is_ookla_anchored</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,9 +1024,13 @@
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>True if this cell-hour's QoE values are model-generated rather than Ookla-anchored.</t>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True if a real Ookla quarterly average existed to re-centre this cell's simulated hourly values on (~41% of cells). False does not mean 'less real' shape — the hourly SHAPE is simulated either way.</t>
         </is>
       </c>
     </row>
@@ -960,23 +1042,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hour_of_day</t>
+          <t>qoe_hourly_shape_is_simulated</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>100</v>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Always True. Included explicitly so this fact cannot be missed or confused with the anchored/unanchored distinction above. Excluded from ML features (constant, zero information).</t>
         </is>
       </c>
     </row>
@@ -988,7 +1074,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>day_of_week</t>
+          <t>hour_of_day</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1002,9 +1088,13 @@
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1106,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>is_weekend</t>
+          <t>day_of_week</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>int32</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1030,9 +1120,13 @@
       <c r="E22" t="b">
         <v>1</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1138,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>is_peak_period</t>
+          <t>is_weekend</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1058,9 +1152,13 @@
       <c r="E23" t="b">
         <v>1</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1170,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lag_1h_dl_median</t>
+          <t>is_peak_period</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Value of dl_median exactly 1 hour prior (shift(1), leakage-free).</t>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1202,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>lag_2h_dl_median</t>
+          <t>lag_1h_dl_median</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1109,14 +1211,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>98.81</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Value of dl_median exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1234,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lag_24h_dl_median</t>
+          <t>lag_2h_dl_median</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1137,14 +1243,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>85.70999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Value of dl_median exactly 24 hours prior (shift(24), leakage-free).</t>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Value of dl_median exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1266,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_dl_median</t>
+          <t>lag_24h_dl_median</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1165,14 +1275,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>99.40000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Value of dl_median exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1298,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rolling_std_24h_dl_median</t>
+          <t>rolling_mean_24h_dl_median</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1193,14 +1307,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Trailing rolling mean of 24h_dl_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1330,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>lag_1h_dl_median_valid</t>
+          <t>rolling_std_24h_dl_median</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1226,9 +1344,13 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Value of dl_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Trailing rolling standard deviation of 24h_dl_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1362,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lag_2h_dl_median_valid</t>
+          <t>lag_1h_dl_median_valid</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1254,9 +1376,13 @@
       <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Value of dl_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1394,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lag_24h_dl_median_valid</t>
+          <t>lag_2h_dl_median_valid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1282,9 +1408,13 @@
       <c r="E31" t="b">
         <v>1</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Value of dl_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Value of dl_median_valid exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1426,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_dl_median_valid</t>
+          <t>lag_24h_dl_median_valid</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1310,9 +1440,13 @@
       <c r="E32" t="b">
         <v>1</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Value of dl_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1324,23 +1458,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lag_1h_rtt_median</t>
+          <t>rolling_mean_24h_dl_median_valid</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Value of rtt_median exactly 1 hour prior (shift(1), leakage-free).</t>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Trailing rolling mean of 24h_dl_median_valid, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1490,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lag_2h_rtt_median</t>
+          <t>lag_1h_rtt_median</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1361,14 +1499,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>98.81</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Value of rtt_median exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1522,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lag_24h_rtt_median</t>
+          <t>lag_2h_rtt_median</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1389,14 +1531,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>85.70999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Value of rtt_median exactly 24 hours prior (shift(24), leakage-free).</t>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Value of rtt_median exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1554,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_rtt_median</t>
+          <t>lag_24h_rtt_median</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1417,14 +1563,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>99.40000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Value of rtt_median exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1586,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rolling_std_24h_rtt_median</t>
+          <t>rolling_mean_24h_rtt_median</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1445,14 +1595,18 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Trailing rolling mean of 24h_rtt_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1618,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>lag_1h_rtt_median_valid</t>
+          <t>rolling_std_24h_rtt_median</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1478,9 +1632,13 @@
       <c r="E38" t="b">
         <v>1</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Value of rtt_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Trailing rolling standard deviation of 24h_rtt_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1650,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lag_2h_rtt_median_valid</t>
+          <t>lag_1h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1506,9 +1664,13 @@
       <c r="E39" t="b">
         <v>1</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Value of rtt_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1682,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lag_24h_rtt_median_valid</t>
+          <t>lag_2h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1534,9 +1696,13 @@
       <c r="E40" t="b">
         <v>1</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Value of rtt_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Value of rtt_median_valid exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1714,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_rtt_median_valid</t>
+          <t>lag_24h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1562,9 +1728,13 @@
       <c r="E41" t="b">
         <v>1</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1 if the corresponding lag/rolling column is backed by real history, 0 during warm-up (NaN).</t>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Value of rtt_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1576,23 +1746,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>qoe_trend_1h</t>
+          <t>rolling_mean_24h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Trailing rolling mean of 24h_rtt_median_valid, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1778,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>in_warmup_window</t>
+          <t>qoe_trend_1h</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1810,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>in_warmup_window</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1646,9 +1824,13 @@
       <c r="E44" t="b">
         <v>1</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1842,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1674,9 +1856,13 @@
       <c r="E45" t="b">
         <v>1</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1874,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1702,9 +1888,13 @@
       <c r="E46" t="b">
         <v>1</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1906,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1730,9 +1920,13 @@
       <c r="E47" t="b">
         <v>1</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1938,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1758,9 +1952,13 @@
       <c r="E48" t="b">
         <v>1</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1970,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1786,9 +1984,13 @@
       <c r="E49" t="b">
         <v>1</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -1800,12 +2002,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1814,9 +2016,13 @@
       <c r="E50" t="b">
         <v>1</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -1828,12 +2034,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1842,9 +2048,13 @@
       <c r="E51" t="b">
         <v>1</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -1856,7 +2066,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1870,9 +2080,13 @@
       <c r="E52" t="b">
         <v>1</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -1884,12 +2098,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1898,9 +2112,13 @@
       <c r="E53" t="b">
         <v>1</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -1912,12 +2130,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1926,9 +2144,13 @@
       <c r="E54" t="b">
         <v>1</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -1940,12 +2162,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1954,9 +2176,13 @@
       <c r="E55" t="b">
         <v>1</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -1968,12 +2194,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1982,9 +2208,13 @@
       <c r="E56" t="b">
         <v>1</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2226,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2010,9 +2240,13 @@
       <c r="E57" t="b">
         <v>1</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2258,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2038,9 +2272,13 @@
       <c r="E58" t="b">
         <v>1</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2290,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2066,9 +2304,13 @@
       <c r="E59" t="b">
         <v>1</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2322,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2094,9 +2336,13 @@
       <c r="E60" t="b">
         <v>1</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2354,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2122,9 +2368,13 @@
       <c r="E61" t="b">
         <v>1</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2386,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2150,9 +2400,13 @@
       <c r="E62" t="b">
         <v>1</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2418,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2178,9 +2432,13 @@
       <c r="E63" t="b">
         <v>1</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F63" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2450,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2206,9 +2464,13 @@
       <c r="E64" t="b">
         <v>1</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
@@ -2220,12 +2482,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2234,9 +2496,13 @@
       <c r="E65" t="b">
         <v>1</v>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2514,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2262,9 +2528,13 @@
       <c r="E66" t="b">
         <v>1</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>WorldPop-derived residential population estimate for the cell.</t>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2546,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2290,9 +2560,13 @@
       <c r="E67" t="b">
         <v>1</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2578,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2318,9 +2592,13 @@
       <c r="E68" t="b">
         <v>1</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density).</t>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2610,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2346,9 +2624,13 @@
       <c r="E69" t="b">
         <v>1</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2642,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>demand_pressure_base</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2374,9 +2656,13 @@
       <c r="E70" t="b">
         <v>1</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2674,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>demand_pressure_index_pre_spatial</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2402,9 +2688,13 @@
       <c r="E71" t="b">
         <v>1</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2706,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>spatial_lag_dl_median</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2430,9 +2720,13 @@
       <c r="E72" t="b">
         <v>1</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp.</t>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2738,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>spatial_var_dl_median</t>
+          <t>demand_pressure_base</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2458,9 +2752,13 @@
       <c r="E73" t="b">
         <v>1</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2770,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>spatial_lag_rtt_median</t>
+          <t>demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2486,9 +2784,17 @@
       <c r="E74" t="b">
         <v>1</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp.</t>
+      <c r="F74" t="b">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>demand_pressure_base plus a historical-QoE component. Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2806,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>spatial_var_rtt_median</t>
+          <t>spatial_lag_dl_median</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2512,11 +2818,15 @@
         <v>100</v>
       </c>
       <c r="E75" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2838,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>spatial_lag_population_night</t>
+          <t>spatial_var_dl_median</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2542,9 +2852,13 @@
       <c r="E76" t="b">
         <v>1</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp.</t>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor variance of dl_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2870,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>spatial_var_population_night</t>
+          <t>spatial_lag_rtt_median</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2568,11 +2882,15 @@
         <v>100</v>
       </c>
       <c r="E77" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2902,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
+          <t>spatial_var_rtt_median</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2598,9 +2916,13 @@
       <c r="E78" t="b">
         <v>1</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp.</t>
+      <c r="F78" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor variance of rtt_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2934,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>spatial_var_demand_pressure_index_pre_spatial</t>
+          <t>spatial_lag_population_night</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2626,9 +2948,13 @@
       <c r="E79" t="b">
         <v>1</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2966,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>demand_pressure_index</t>
+          <t>spatial_var_population_night</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2654,9 +2980,13 @@
       <c r="E80" t="b">
         <v>1</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0-100 composite demand pressure (population, POI, built-up, roads, historical QoE, nearby demand).</t>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor variance of population_night at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2998,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>spatial_rolling_mean_24h_dl_median</t>
+          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2682,9 +3012,13 @@
       <c r="E81" t="b">
         <v>1</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2696,7 +3030,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>gi_star_zscore_rtt_median</t>
+          <t>spatial_var_demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2710,9 +3044,13 @@
       <c r="E82" t="b">
         <v>1</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Getis-Ord Gi* z-score for latency (esda.G_Local, star=True).</t>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Row-standardized H3 1-ring neighbor variance of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2724,12 +3062,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>gi_star_pvalue_rtt_median</t>
+          <t>demand_pressure_index</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>float32</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2738,9 +3076,17 @@
       <c r="E83" t="b">
         <v>1</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Final spatially-smoothed demand pressure index. Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
         </is>
       </c>
     </row>
@@ -2752,12 +3098,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>hotspot_category_rtt_median</t>
+          <t>spatial_rolling_mean_24h_dl_median</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2766,9 +3112,13 @@
       <c r="E84" t="b">
         <v>1</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Hot/cold spot classification at 90/95/99% confidence (esda.G_Local p-values).</t>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -2780,7 +3130,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>local_moran_i_rtt_median</t>
+          <t>gi_star_zscore_rtt_median</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2794,9 +3144,13 @@
       <c r="E85" t="b">
         <v>1</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Real Getis-Ord Gi* z-score for latency (esda.G_Local, star=True) — the full Gi* expectation/variance formulation, not a plain standardized neighbor average.</t>
         </is>
       </c>
     </row>
@@ -2808,12 +3162,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>local_moran_pvalue_rtt_median</t>
+          <t>gi_star_pvalue_rtt_median</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>float32</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2822,9 +3176,13 @@
       <c r="E86" t="b">
         <v>1</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Permutation-based p-value (99 permutations) for the Getis-Ord Gi* statistic on rtt_median.</t>
         </is>
       </c>
     </row>
@@ -2836,7 +3194,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>local_moran_quadrant_rtt_median</t>
+          <t>hotspot_category_rtt_median</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2850,9 +3208,13 @@
       <c r="E87" t="b">
         <v>1</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>HH/LH/LL/HL spatial cluster/outlier classification (esda.Moran_Local).</t>
+      <c r="F87" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Hot/cold spot classification at 90/95/99% confidence, from real esda.G_Local p-values.</t>
         </is>
       </c>
     </row>
@@ -2864,7 +3226,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>historical_hotspot_freq_rtt_median</t>
+          <t>local_moran_i_rtt_median</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2878,9 +3240,13 @@
       <c r="E88" t="b">
         <v>1</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real hotspot.</t>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Local Moran's I statistic value for rtt_median (real esda.Moran_Local).</t>
         </is>
       </c>
     </row>
@@ -2892,7 +3258,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>target_qoe_score</t>
+          <t>local_moran_pvalue_rtt_median</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2904,11 +3270,15 @@
         <v>100</v>
       </c>
       <c r="E89" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Composite 0-100 QoE score (ITU-inspired).</t>
+        <v>1</v>
+      </c>
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Permutation-based p-value (99 permutations) for Local Moran's I on rtt_median.</t>
         </is>
       </c>
     </row>
@@ -2920,23 +3290,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>target_mos</t>
+          <t>local_moran_quadrant_rtt_median</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>100</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Mean Opinion Score estimate (1.0-5.0).</t>
+        <v>1</v>
+      </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>HH/LH/LL/HL spatial cluster/outlier classification (real esda.Moran_Local).</t>
         </is>
       </c>
     </row>
@@ -2948,23 +3322,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>historical_hotspot_freq_rtt_median</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>100</v>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Binary degradation flag (dl below threshold OR rtt above threshold).</t>
+        <v>1</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real (esda-confirmed) hotspot.</t>
         </is>
       </c>
     </row>
@@ -2976,12 +3354,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>target_qoe_index</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2990,9 +3368,13 @@
       <c r="E92" t="b">
         <v>0</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0=normal, 1=degraded, 2=severe.</t>
+      <c r="F92" t="b">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3386,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>qoe_confidence_score</t>
+          <t>target_service_quality_1to5</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3016,28 +3398,32 @@
         <v>100</v>
       </c>
       <c r="E93" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>target_is_degraded</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3046,21 +3432,25 @@
       <c r="E94" t="b">
         <v>0</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+      <c r="F94" t="b">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>target_degradation_class</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3072,23 +3462,27 @@
         <v>100</v>
       </c>
       <c r="E95" t="b">
-        <v>1</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F95" t="b">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>qoe_confidence_score</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3102,21 +3496,25 @@
       <c r="E96" t="b">
         <v>1</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>target_is_degraded_next_1h</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3125,98 +3523,114 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E97" t="b">
-        <v>1</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F97" t="b">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>target_degradation_class_next_1h</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E98" t="b">
-        <v>1</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+        <v>0</v>
+      </c>
+      <c r="F98" t="b">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>3-class version of the next-hour forecast target.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>target_qoe_index_next_1h</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E99" t="b">
-        <v>1</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F99" t="b">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Continuous version of the next-hour forecast target.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>target_next_1h_valid</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>100</v>
       </c>
       <c r="E100" t="b">
-        <v>1</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+        <v>0</v>
+      </c>
+      <c r="F100" t="b">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3642,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3242,9 +3656,13 @@
       <c r="E101" t="b">
         <v>1</v>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3674,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3270,9 +3688,13 @@
       <c r="E102" t="b">
         <v>1</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F102" t="b">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3706,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3298,9 +3720,13 @@
       <c r="E103" t="b">
         <v>1</v>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3738,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3326,9 +3752,13 @@
       <c r="E104" t="b">
         <v>1</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+      <c r="F104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3770,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -3354,9 +3784,13 @@
       <c r="E105" t="b">
         <v>1</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3802,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -3382,9 +3816,13 @@
       <c r="E106" t="b">
         <v>1</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3834,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3410,9 +3848,13 @@
       <c r="E107" t="b">
         <v>1</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3866,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3438,9 +3880,13 @@
       <c r="E108" t="b">
         <v>1</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3898,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -3466,9 +3912,13 @@
       <c r="E109" t="b">
         <v>1</v>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3930,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3494,9 +3944,13 @@
       <c r="E110" t="b">
         <v>1</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3962,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3522,9 +3976,13 @@
       <c r="E111" t="b">
         <v>1</v>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3994,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3550,9 +4008,13 @@
       <c r="E112" t="b">
         <v>1</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -3564,12 +4026,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3578,9 +4040,13 @@
       <c r="E113" t="b">
         <v>1</v>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -3592,12 +4058,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -3606,9 +4072,13 @@
       <c r="E114" t="b">
         <v>1</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -3620,7 +4090,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3634,9 +4104,13 @@
       <c r="E115" t="b">
         <v>1</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -3648,12 +4122,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -3662,9 +4136,13 @@
       <c r="E116" t="b">
         <v>1</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -3676,12 +4154,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -3690,9 +4168,13 @@
       <c r="E117" t="b">
         <v>1</v>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>WorldPop-derived residential population estimate for the cell.</t>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -3704,12 +4186,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3718,9 +4200,13 @@
       <c r="E118" t="b">
         <v>1</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="F118" t="b">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -3732,7 +4218,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3746,9 +4232,13 @@
       <c r="E119" t="b">
         <v>1</v>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density).</t>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -3760,12 +4250,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3774,21 +4264,25 @@
       <c r="E120" t="b">
         <v>1</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>row_id</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3800,207 +4294,1743 @@
         <v>100</v>
       </c>
       <c r="E121" t="b">
-        <v>0</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
+        <v>1</v>
+      </c>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D122" t="n">
         <v>100</v>
       </c>
       <c r="E122" t="b">
-        <v>0</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+        <v>1</v>
+      </c>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D123" t="n">
         <v>100</v>
       </c>
       <c r="E123" t="b">
-        <v>0</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
+        <v>1</v>
+      </c>
+      <c r="F123" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>target_qoe_score</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D124" t="n">
         <v>100</v>
       </c>
       <c r="E124" t="b">
-        <v>0</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Composite 0-100 QoE score (ITU-inspired).</t>
+        <v>1</v>
+      </c>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>target_mos</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D125" t="n">
         <v>100</v>
       </c>
       <c r="E125" t="b">
-        <v>0</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Mean Opinion Score estimate (1.0-5.0).</t>
+        <v>1</v>
+      </c>
+      <c r="F125" t="b">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D126" t="n">
         <v>100</v>
       </c>
       <c r="E126" t="b">
-        <v>0</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Binary degradation flag (dl below threshold OR rtt above threshold).</t>
+        <v>1</v>
+      </c>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>100</v>
       </c>
       <c r="E127" t="b">
-        <v>0</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>0=normal, 1=degraded, 2=severe.</t>
+        <v>1</v>
+      </c>
+      <c r="F127" t="b">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>population_day</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>100</v>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+      <c r="F128" t="b">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cell_static_features</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>population_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>100</v>
+      </c>
+      <c r="E129" t="b">
+        <v>1</v>
+      </c>
+      <c r="F129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>h3_index</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>100</v>
+      </c>
+      <c r="E130" t="b">
+        <v>1</v>
+      </c>
+      <c r="F130" t="b">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>tower_count</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>100</v>
+      </c>
+      <c r="E131" t="b">
+        <v>1</v>
+      </c>
+      <c r="F131" t="b">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>opencellid_record_count</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>100</v>
+      </c>
+      <c r="E132" t="b">
+        <v>1</v>
+      </c>
+      <c r="F132" t="b">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>tower_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>100</v>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+      <c r="F133" t="b">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>dist_to_nearest_tower_m</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>100</v>
+      </c>
+      <c r="E134" t="b">
+        <v>1</v>
+      </c>
+      <c r="F134" t="b">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>tower_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>100</v>
+      </c>
+      <c r="E135" t="b">
+        <v>1</v>
+      </c>
+      <c r="F135" t="b">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>tower_source</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>100</v>
+      </c>
+      <c r="E136" t="b">
+        <v>1</v>
+      </c>
+      <c r="F136" t="b">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>building_count</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>100</v>
+      </c>
+      <c r="E137" t="b">
+        <v>1</v>
+      </c>
+      <c r="F137" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>total_building_area_m2</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>100</v>
+      </c>
+      <c r="E138" t="b">
+        <v>1</v>
+      </c>
+      <c r="F138" t="b">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Real summed footprint area (m^2) per cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>built_up_ratio</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>100</v>
+      </c>
+      <c r="E139" t="b">
+        <v>1</v>
+      </c>
+      <c r="F139" t="b">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>building_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>100</v>
+      </c>
+      <c r="E140" t="b">
+        <v>1</v>
+      </c>
+      <c r="F140" t="b">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>building_count / real cell area (km^2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>avg_building_footprint_m2</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>100</v>
+      </c>
+      <c r="E141" t="b">
+        <v>1</v>
+      </c>
+      <c r="F141" t="b">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>total_building_area_m2 / building_count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>building_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>100</v>
+      </c>
+      <c r="E142" t="b">
+        <v>1</v>
+      </c>
+      <c r="F142" t="b">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>poi_education_count</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>100</v>
+      </c>
+      <c r="E143" t="b">
+        <v>1</v>
+      </c>
+      <c r="F143" t="b">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>poi_healthcare_count</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>100</v>
+      </c>
+      <c r="E144" t="b">
+        <v>1</v>
+      </c>
+      <c r="F144" t="b">
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>poi_retail_food_count</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>100</v>
+      </c>
+      <c r="E145" t="b">
+        <v>1</v>
+      </c>
+      <c r="F145" t="b">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>poi_office_count</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>100</v>
+      </c>
+      <c r="E146" t="b">
+        <v>1</v>
+      </c>
+      <c r="F146" t="b">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: tagged office=*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>poi_recreation_count</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>100</v>
+      </c>
+      <c r="E147" t="b">
+        <v>1</v>
+      </c>
+      <c r="F147" t="b">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>road_length_m</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>100</v>
+      </c>
+      <c r="E148" t="b">
+        <v>1</v>
+      </c>
+      <c r="F148" t="b">
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>road_density_km_per_km2</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>100</v>
+      </c>
+      <c r="E149" t="b">
+        <v>1</v>
+      </c>
+      <c r="F149" t="b">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>intersection_count</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>100</v>
+      </c>
+      <c r="E150" t="b">
+        <v>1</v>
+      </c>
+      <c r="F150" t="b">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Real OSM road-network node count per cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>intersection_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>100</v>
+      </c>
+      <c r="E151" t="b">
+        <v>1</v>
+      </c>
+      <c r="F151" t="b">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>intersection_count / real cell area (km^2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>dist_to_nearest_transit_m</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>100</v>
+      </c>
+      <c r="E152" t="b">
+        <v>1</v>
+      </c>
+      <c r="F152" t="b">
+        <v>1</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>poi_transport_stop_count</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>100</v>
+      </c>
+      <c r="E153" t="b">
+        <v>1</v>
+      </c>
+      <c r="F153" t="b">
+        <v>1</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>osm_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>100</v>
+      </c>
+      <c r="E154" t="b">
+        <v>1</v>
+      </c>
+      <c r="F154" t="b">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>population_night</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>100</v>
+      </c>
+      <c r="E155" t="b">
+        <v>1</v>
+      </c>
+      <c r="F155" t="b">
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>population_density_per_km2</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>100</v>
+      </c>
+      <c r="E156" t="b">
+        <v>1</v>
+      </c>
+      <c r="F156" t="b">
+        <v>1</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>population_day</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>100</v>
+      </c>
+      <c r="E157" t="b">
+        <v>1</v>
+      </c>
+      <c r="F157" t="b">
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>population_is_synthetic</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>100</v>
+      </c>
+      <c r="E158" t="b">
+        <v>1</v>
+      </c>
+      <c r="F158" t="b">
+        <v>1</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ookla_dl_mbps</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E159" t="b">
+        <v>1</v>
+      </c>
+      <c r="F159" t="b">
+        <v>1</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>REAL Ookla tests-weighted mean download speed (Mbps) for the cell, static/quarterly. NaN where no tile coverage exists (not imputed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ookla_rtt_ms</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E160" t="b">
+        <v>1</v>
+      </c>
+      <c r="F160" t="b">
+        <v>1</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>REAL Ookla tests-weighted mean latency (ms) for the cell, static/quarterly. NaN where no tile coverage exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ookla_tests</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E161" t="b">
+        <v>1</v>
+      </c>
+      <c r="F161" t="b">
+        <v>1</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>REAL summed Ookla test count backing ookla_dl_mbps/ookla_rtt_ms for the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>has_real_ookla_label</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>100</v>
+      </c>
+      <c r="E162" t="b">
+        <v>1</v>
+      </c>
+      <c r="F162" t="b">
+        <v>1</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>True if ookla_dl_mbps is non-null — i.e. this row has a REAL label usable for training in cell_static_qoe_baseline.parquet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>cell_static_qoe_baseline</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>qoe_risk_label</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E163" t="b">
+        <v>1</v>
+      </c>
+      <c r="F163" t="b">
+        <v>1</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>high_risk/moderate_risk/low_risk from REAL ookla_dl_mbps thresholds. None where has_real_ookla_label is False (deliberately not guessed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>qoe_targets</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>100</v>
+      </c>
+      <c r="E164" t="b">
+        <v>0</v>
+      </c>
+      <c r="F164" t="b">
+        <v>0</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>h3_index</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>100</v>
+      </c>
+      <c r="E165" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" t="b">
+        <v>0</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>datetime64[us]</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>100</v>
+      </c>
+      <c r="E166" t="b">
+        <v>0</v>
+      </c>
+      <c r="F166" t="b">
+        <v>0</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>target_qoe_index</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>100</v>
+      </c>
+      <c r="E167" t="b">
+        <v>0</v>
+      </c>
+      <c r="F167" t="b">
+        <v>0</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>target_service_quality_1to5</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>100</v>
+      </c>
+      <c r="E168" t="b">
+        <v>0</v>
+      </c>
+      <c r="F168" t="b">
+        <v>0</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>target_is_degraded</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>100</v>
+      </c>
+      <c r="E169" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" t="b">
+        <v>0</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>target_degradation_class</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>100</v>
+      </c>
+      <c r="E170" t="b">
+        <v>0</v>
+      </c>
+      <c r="F170" t="b">
+        <v>0</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>target_is_degraded_next_1h</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E171" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" t="b">
+        <v>0</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>target_degradation_class_next_1h</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E172" t="b">
+        <v>0</v>
+      </c>
+      <c r="F172" t="b">
+        <v>0</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>3-class version of the next-hour forecast target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>target_qoe_index_next_1h</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E173" t="b">
+        <v>0</v>
+      </c>
+      <c r="F173" t="b">
+        <v>0</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Continuous version of the next-hour forecast target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>target_next_1h_valid</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>100</v>
+      </c>
+      <c r="E174" t="b">
+        <v>0</v>
+      </c>
+      <c r="F174" t="b">
+        <v>0</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
         <is>
           <t>qoe_confidence_score</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>float64</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>100</v>
-      </c>
-      <c r="E128" t="b">
-        <v>1</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>See src/data_preprocessing/ module docstrings.</t>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>100</v>
+      </c>
+      <c r="E175" t="b">
+        <v>1</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
         </is>
       </c>
     </row>

--- a/data/outputs/feature_dictionary.xlsx
+++ b/data/outputs/feature_dictionary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,7 +966,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Real Ookla test count where a real anchor exists for the cell; Poisson-simulated otherwise. Represents measurement VOLUME, not the outcome — safe as a feature in either target mode.</t>
+          <t>Simulated HOURLY-equivalent test count. For Ookla-anchored cells this is Poisson-sampled around an hourly rate derived from the REAL quarterly total (ookla_quarter_test_count / ~2160 hours, scaled by demand), NOT the quarterly total itself repeated per hour (that was a bug — see CHANGELOG). Represents measurement VOLUME, not the outcome — safe as a feature in either target mode.</t>
         </is>
       </c>
     </row>
@@ -1010,16 +1010,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qoe_level_is_ookla_anchored</t>
+          <t>ookla_quarter_test_count</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>57.78</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -1030,7 +1030,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>True if a real Ookla quarterly average existed to re-centre this cell's simulated hourly values on (~41% of cells). False does not mean 'less real' shape — the hourly SHAPE is simulated either way.</t>
+          <t>REAL Ookla quarterly test count for this cell (constant across all 168 simulated hours by definition — it is a QUARTERLY total, never a per-hour figure). NaN if the cell has no Ookla tile coverage.</t>
         </is>
       </c>
     </row>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>qoe_hourly_shape_is_simulated</t>
+          <t>ookla_quarter_device_count</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>57.78</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Always True. Included explicitly so this fact cannot be missed or confused with the anchored/unanchored distinction above. Excluded from ML features (constant, zero information).</t>
+          <t>REAL Ookla quarterly unique-device count for this cell (constant across all 168 simulated hours; quarterly, not hourly). NaN if unavailable in the source tile or no coverage exists.</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hour_of_day</t>
+          <t>qoe_baseline_source</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1094,7 +1094,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Human-readable provenance string: 'ookla_q4_2024_static_anchor' or 'no_real_anchor_simulated_only'. Complements the qoe_level_is_ookla_anchored boolean.</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>day_of_week</t>
+          <t>qoe_level_is_ookla_anchored</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1126,7 +1126,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>True if a real Ookla quarterly average existed to re-centre this cell's simulated hourly values on (~41% of cells). False does not mean 'less real' shape — the hourly SHAPE is simulated either way.</t>
         </is>
       </c>
     </row>
@@ -1138,27 +1138,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>is_weekend</t>
+          <t>qoe_hourly_shape_is_simulated</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>100</v>
       </c>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Always True. Included explicitly so this fact cannot be missed or confused with the anchored/unanchored distinction above. Excluded from ML features (constant, zero information).</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>is_peak_period</t>
+          <t>ridership_daily_surge_factor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1190,7 +1190,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Real daily ridership-derived demand multiplier (normalized to the selected week's mean), summed only over Klang-Valley-relevant transit modes (national/inter-city services like ETS, Intercity, Komuter Utara, and Tebrau are excluded). Previously folded silently into the hourly formula with no standalone column; now exported directly so it can be inspected or used as its own feature.</t>
         </is>
       </c>
     </row>
@@ -1202,16 +1202,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>lag_1h_dl_median</t>
+          <t>hour_of_day</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int32</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -1222,7 +1222,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Value of dl_median exactly 1 hour prior (shift(1), leakage-free).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1234,16 +1234,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lag_2h_dl_median</t>
+          <t>day_of_week</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int32</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>98.81</v>
+        <v>100</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Value of dl_median exactly 2 hours prior (shift(2), leakage-free).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1266,16 +1266,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lag_24h_dl_median</t>
+          <t>is_weekend</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -1286,7 +1286,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Value of dl_median exactly 24 hours prior (shift(24), leakage-free).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1298,16 +1298,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_dl_median</t>
+          <t>is_peak_period</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -1318,7 +1318,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Trailing rolling mean of 24h_dl_median, computed after shift(1) (leakage-free).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rolling_std_24h_dl_median</t>
+          <t>lag_1h_dl_median</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -1350,7 +1350,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Trailing rolling standard deviation of 24h_dl_median, computed after shift(1) (leakage-free).</t>
+          <t>Value of dl_median exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lag_1h_dl_median_valid</t>
+          <t>lag_2h_dl_median</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>100</v>
+        <v>98.81</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
@@ -1382,7 +1382,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Value of dl_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
+          <t>Value of dl_median exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1394,16 +1394,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lag_2h_dl_median_valid</t>
+          <t>lag_24h_dl_median</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -1414,7 +1414,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Value of dl_median_valid exactly 2 hours prior (shift(2), leakage-free).</t>
+          <t>Value of dl_median exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lag_24h_dl_median_valid</t>
+          <t>rolling_mean_24h_dl_median</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -1446,7 +1446,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Value of dl_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
+          <t>Trailing rolling mean of 24h_dl_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_dl_median_valid</t>
+          <t>rolling_std_24h_dl_median</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1478,7 +1478,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Trailing rolling mean of 24h_dl_median_valid, computed after shift(1) (leakage-free).</t>
+          <t>Trailing rolling standard deviation of 24h_dl_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1490,16 +1490,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lag_1h_rtt_median</t>
+          <t>lag_1h_dl_median_valid</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -1510,7 +1510,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Value of rtt_median exactly 1 hour prior (shift(1), leakage-free).</t>
+          <t>Value of dl_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1522,16 +1522,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lag_2h_rtt_median</t>
+          <t>lag_2h_dl_median_valid</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>98.81</v>
+        <v>100</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1542,7 +1542,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Value of rtt_median exactly 2 hours prior (shift(2), leakage-free).</t>
+          <t>Value of dl_median_valid exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1554,16 +1554,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lag_24h_rtt_median</t>
+          <t>lag_24h_dl_median_valid</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -1574,7 +1574,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Value of rtt_median exactly 24 hours prior (shift(24), leakage-free).</t>
+          <t>Value of dl_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1586,16 +1586,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_rtt_median</t>
+          <t>rolling_mean_24h_dl_median_valid</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1606,7 +1606,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Trailing rolling mean of 24h_rtt_median, computed after shift(1) (leakage-free).</t>
+          <t>Trailing rolling mean of 24h_dl_median_valid, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rolling_std_24h_rtt_median</t>
+          <t>lag_1h_rtt_median</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1638,7 +1638,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Trailing rolling standard deviation of 24h_rtt_median, computed after shift(1) (leakage-free).</t>
+          <t>Value of rtt_median exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1650,16 +1650,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lag_1h_rtt_median_valid</t>
+          <t>lag_2h_rtt_median</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>100</v>
+        <v>98.81</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1670,7 +1670,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Value of rtt_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
+          <t>Value of rtt_median exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1682,16 +1682,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lag_2h_rtt_median_valid</t>
+          <t>lag_24h_rtt_median</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
@@ -1702,7 +1702,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Value of rtt_median_valid exactly 2 hours prior (shift(2), leakage-free).</t>
+          <t>Value of rtt_median exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1714,16 +1714,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>lag_24h_rtt_median_valid</t>
+          <t>rolling_mean_24h_rtt_median</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
@@ -1734,7 +1734,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Value of rtt_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
+          <t>Trailing rolling mean of 24h_rtt_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>rolling_mean_24h_rtt_median_valid</t>
+          <t>rolling_std_24h_rtt_median</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1766,7 +1766,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Trailing rolling mean of 24h_rtt_median_valid, computed after shift(1) (leakage-free).</t>
+          <t>Trailing rolling standard deviation of 24h_rtt_median, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1778,16 +1778,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>qoe_trend_1h</t>
+          <t>lag_1h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1798,7 +1798,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Value of rtt_median_valid exactly 1 hour prior (shift(1), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>in_warmup_window</t>
+          <t>lag_2h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1830,7 +1830,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Value of rtt_median_valid exactly 2 hours prior (shift(2), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>lag_24h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1862,7 +1862,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+          <t>Value of rtt_median_valid exactly 24 hours prior (shift(24), leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>opencellid_record_count</t>
+          <t>rolling_mean_24h_rtt_median_valid</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1894,7 +1894,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+          <t>Trailing rolling mean of 24h_rtt_median_valid, computed after shift(1) (leakage-free).</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>qoe_trend_1h</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>in_warmup_window</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1958,7 +1958,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1990,7 +1990,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tower_source</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2022,7 +2022,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2054,7 +2054,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2086,7 +2086,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Real summed footprint area (m^2) per cell.</t>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2118,7 +2118,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2150,7 +2150,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>building_count / real cell area (km^2).</t>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2182,7 +2182,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>total_building_area_m2 / building_count.</t>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2214,7 +2214,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2246,7 +2246,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2278,7 +2278,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2310,7 +2310,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2342,7 +2342,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Real OSM POI count: tagged office=*.</t>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2374,7 +2374,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2406,7 +2406,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2438,7 +2438,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>road_length_m / 1000 / real cell area (km^2).</t>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2470,7 +2470,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Real OSM road-network node count per cell.</t>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2502,7 +2502,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>intersection_count / real cell area (km^2).</t>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2566,7 +2566,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2598,7 +2598,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2630,7 +2630,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2662,7 +2662,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>population_night / real cell area (km^2, projected CRS).</t>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2694,7 +2694,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>demand_pressure_base</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2758,7 +2758,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>demand_pressure_index_pre_spatial</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2787,14 +2787,10 @@
       <c r="F74" t="b">
         <v>1</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>demand_pressure_base plus a historical-QoE component. Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2802,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>spatial_lag_dl_median</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2818,7 +2814,7 @@
         <v>100</v>
       </c>
       <c r="E75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -2826,7 +2822,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp (real libpysal weights).</t>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2834,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>spatial_var_dl_median</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2858,7 +2854,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of dl_median at the same timestamp (real libpysal weights).</t>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2866,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>spatial_lag_rtt_median</t>
+          <t>demand_pressure_base</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2882,7 +2878,7 @@
         <v>100</v>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -2890,7 +2886,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp (real libpysal weights).</t>
+          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>spatial_var_rtt_median</t>
+          <t>demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2919,10 +2915,14 @@
       <c r="F78" t="b">
         <v>1</v>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of rtt_median at the same timestamp (real libpysal weights).</t>
+          <t>demand_pressure_base plus a historical-QoE component. Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>spatial_lag_population_night</t>
+          <t>spatial_lag_dl_median</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2946,7 +2946,7 @@
         <v>100</v>
       </c>
       <c r="E79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -2954,7 +2954,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>spatial_var_population_night</t>
+          <t>spatial_var_dl_median</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2986,7 +2986,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of population_night at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor variance of dl_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
+          <t>spatial_lag_rtt_median</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3010,7 +3010,7 @@
         <v>100</v>
       </c>
       <c r="E81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>spatial_var_demand_pressure_index_pre_spatial</t>
+          <t>spatial_var_rtt_median</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3050,7 +3050,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor variance of rtt_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>demand_pressure_index</t>
+          <t>spatial_lag_population_night</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3079,14 +3079,10 @@
       <c r="F83" t="b">
         <v>1</v>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Final spatially-smoothed demand pressure index. Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
+          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3094,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>spatial_rolling_mean_24h_dl_median</t>
+          <t>spatial_var_population_night</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3118,7 +3114,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Row-standardized H3 1-ring neighbor variance of population_night at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3126,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>gi_star_zscore_rtt_median</t>
+          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3150,7 +3146,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Real Getis-Ord Gi* z-score for latency (esda.G_Local, star=True) — the full Gi* expectation/variance formulation, not a plain standardized neighbor average.</t>
+          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3158,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>gi_star_pvalue_rtt_median</t>
+          <t>spatial_var_demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>float32</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3182,7 +3178,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Permutation-based p-value (99 permutations) for the Getis-Ord Gi* statistic on rtt_median.</t>
+          <t>Row-standardized H3 1-ring neighbor variance of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3190,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>hotspot_category_rtt_median</t>
+          <t>demand_pressure_index</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3211,10 +3207,14 @@
       <c r="F87" t="b">
         <v>1</v>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Hot/cold spot classification at 90/95/99% confidence, from real esda.G_Local p-values.</t>
+          <t>Final spatially-smoothed demand pressure index. Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>local_moran_i_rtt_median</t>
+          <t>spatial_rolling_mean_24h_dl_median</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3246,7 +3246,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Local Moran's I statistic value for rtt_median (real esda.Moran_Local).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>local_moran_pvalue_rtt_median</t>
+          <t>gi_star_zscore_rtt_median</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3278,7 +3278,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Permutation-based p-value (99 permutations) for Local Moran's I on rtt_median.</t>
+          <t>Real Getis-Ord Gi* z-score for latency (esda.G_Local, star=True) — the full Gi* expectation/variance formulation, not a plain standardized neighbor average.</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>local_moran_quadrant_rtt_median</t>
+          <t>gi_star_pvalue_rtt_median</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float32</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3310,7 +3310,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>HH/LH/LL/HL spatial cluster/outlier classification (real esda.Moran_Local).</t>
+          <t>Permutation-based p-value (99 permutations) for the Getis-Ord Gi* statistic on rtt_median.</t>
         </is>
       </c>
     </row>
@@ -3322,27 +3322,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>historical_hotspot_freq_rtt_median</t>
+          <t>hotspot_category_rtt_median</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>100</v>
       </c>
       <c r="E91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real (esda-confirmed) hotspot.</t>
+          <t>Hot/cold spot classification at 90/95/99% confidence, from real esda.G_Local p-values.</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>target_qoe_index</t>
+          <t>local_moran_i_rtt_median</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3366,15 +3366,15 @@
         <v>100</v>
       </c>
       <c r="E92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
+          <t>Local Moran's I statistic value for rtt_median (real esda.Moran_Local).</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>target_service_quality_1to5</t>
+          <t>local_moran_pvalue_rtt_median</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3398,15 +3398,15 @@
         <v>100</v>
       </c>
       <c r="E93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
+          <t>Permutation-based p-value (99 permutations) for Local Moran's I on rtt_median.</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>local_moran_quadrant_rtt_median</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3438,7 +3438,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
+          <t>HH/LH/LL/HL spatial cluster/outlier classification (real esda.Moran_Local).</t>
         </is>
       </c>
     </row>
@@ -3450,27 +3450,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>historical_hotspot_freq_rtt_median</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>100</v>
       </c>
       <c r="E95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
+          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real (esda-confirmed) hotspot.</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>qoe_confidence_score</t>
+          <t>hotspot_category_rtt_median_encoded</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3502,7 +3502,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
+          <t>Ordinal-encoded hotspot confidence band (0=cold_99, 1=cold_95, 2=cold_90, 3=not_significant, 4=hot_90, 5=hot_95, 6=hot_99). ML-compatible integer version of hotspot_category_rtt_median (string, kept for dashboard).</t>
         </is>
       </c>
     </row>
@@ -3514,27 +3514,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>target_is_degraded_next_1h</t>
+          <t>local_moran_quadrant_rtt_median_encoded</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
+          <t>Ordinal-encoded Local Moran's I spatial cluster/outlier class (0=not_significant, 1=LL, 2=LH, 3=HL, 4=HH). ML-compatible integer version of local_moran_quadrant_rtt_median (string, kept for dashboard).</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>target_degradation_class_next_1h</t>
+          <t>target_qoe_index</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
@@ -3566,7 +3566,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3-class version of the next-hour forecast target.</t>
+          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>target_qoe_index_next_1h</t>
+          <t>target_service_quality_1to5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Continuous version of the next-hour forecast target.</t>
+          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>target_next_1h_valid</t>
+          <t>target_is_degraded</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3630,56 +3630,56 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>target_degradation_class</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>100</v>
       </c>
       <c r="E101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>qoe_confidence_score</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3694,51 +3694,51 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+          <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>opencellid_record_count</t>
+          <t>target_is_degraded_next_1h</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>target_degradation_class_next_1h</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3747,30 +3747,30 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>3-class version of the next-hour forecast target.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>target_qoe_index_next_1h</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3779,114 +3779,114 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+          <t>Continuous version of the next-hour forecast target.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>target_next_1h_valid</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>100</v>
       </c>
       <c r="E106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>tower_source</t>
+          <t>priority_exposure_score</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>100</v>
       </c>
       <c r="E107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+          <t>MinMax-scaled population_day floored at 0.01 — the population-exposure component of the Priority Score. Not an ML feature (derived from population_day).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>priority_base_score</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>100</v>
       </c>
       <c r="E108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+          <t>priority_exposure_score × historical_hotspot_freq × max(0.1, qoe_confidence_score) — pre-computed Priority Score base without model risk probability. Dashboard: final_priority = model_predicted_risk × priority_base_score. Not an ML feature.</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -3918,7 +3918,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Real summed footprint area (m^2) per cell.</t>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3930,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -3950,7 +3950,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -3962,12 +3962,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -3982,7 +3982,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>building_count / real cell area (km^2).</t>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4014,7 +4014,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>total_building_area_m2 / building_count.</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4046,7 +4046,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4058,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4078,7 +4078,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4110,7 +4110,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4142,7 +4142,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4174,7 +4174,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Real OSM POI count: tagged office=*.</t>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4186,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4206,7 +4206,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4238,7 +4238,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>road_length_m / 1000 / real cell area (km^2).</t>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4302,7 +4302,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Real OSM road-network node count per cell.</t>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4334,7 +4334,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>intersection_count / real cell area (km^2).</t>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4366,7 +4366,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4398,7 +4398,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4430,7 +4430,7 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4462,7 +4462,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4494,7 +4494,7 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>population_night / real cell area (km^2, projected CRS).</t>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4526,7 +4526,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4558,24 +4558,24 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4590,24 +4590,24 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4622,19 +4622,19 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>opencellid_record_count</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4654,24 +4654,24 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -4686,19 +4686,19 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4718,24 +4718,24 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -4750,24 +4750,24 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>tower_source</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -4782,24 +4782,24 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -4814,19 +4814,19 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>demand_pressure_base</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4846,7 +4846,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Real summed footprint area (m^2) per cell.</t>
+          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -4878,7 +4878,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -4910,7 +4910,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>building_count / real cell area (km^2).</t>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4942,7 +4942,7 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>total_building_area_m2 / building_count.</t>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -4974,7 +4974,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5006,7 +5006,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5038,7 +5038,7 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5070,7 +5070,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5102,7 +5102,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Real OSM POI count: tagged office=*.</t>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5134,7 +5134,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5166,7 +5166,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5198,7 +5198,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>road_length_m / 1000 / real cell area (km^2).</t>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5230,7 +5230,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Real OSM road-network node count per cell.</t>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -5242,12 +5242,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5262,7 +5262,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>intersection_count / real cell area (km^2).</t>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5294,7 +5294,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5326,7 +5326,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5358,7 +5358,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5390,7 +5390,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5402,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5422,7 +5422,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>population_night / real cell area (km^2, projected CRS).</t>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5454,7 +5454,7 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5486,7 +5486,7 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -5498,16 +5498,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ookla_dl_mbps</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E159" t="b">
         <v>1</v>
@@ -5518,7 +5518,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>REAL Ookla tests-weighted mean download speed (Mbps) for the cell, static/quarterly. NaN where no tile coverage exists (not imputed).</t>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ookla_rtt_ms</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E160" t="b">
         <v>1</v>
@@ -5550,7 +5550,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>REAL Ookla tests-weighted mean latency (ms) for the cell, static/quarterly. NaN where no tile coverage exists.</t>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ookla_tests</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E161" t="b">
         <v>1</v>
@@ -5582,7 +5582,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>REAL summed Ookla test count backing ookla_dl_mbps/ookla_rtt_ms for the cell.</t>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>has_real_ookla_label</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -5614,7 +5614,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>True if ookla_dl_mbps is non-null — i.e. this row has a REAL label usable for training in cell_static_qoe_baseline.parquet.</t>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
@@ -5626,16 +5626,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>qoe_risk_label</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E163" t="b">
         <v>1</v>
@@ -5646,147 +5646,147 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>high_risk/moderate_risk/low_risk from REAL ookla_dl_mbps thresholds. None where has_real_ookla_label is False (deliberately not guessed).</t>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>row_id</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D164" t="n">
         <v>100</v>
       </c>
       <c r="E164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D165" t="n">
         <v>100</v>
       </c>
       <c r="E165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>100</v>
       </c>
       <c r="E166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>target_qoe_index</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>100</v>
       </c>
       <c r="E167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>target_service_quality_1to5</t>
+          <t>ookla_dl_mbps</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5795,146 +5795,146 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>100</v>
+        <v>57.78</v>
       </c>
       <c r="E168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
+          <t>REAL Ookla tests-weighted mean download speed (Mbps) for the cell, static/quarterly. NaN where no tile coverage exists (not imputed).</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>ookla_rtt_ms</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>100</v>
+        <v>57.78</v>
       </c>
       <c r="E169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
+          <t>REAL Ookla tests-weighted mean latency (ms) for the cell, static/quarterly. NaN where no tile coverage exists.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>ookla_tests</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>100</v>
+        <v>57.78</v>
       </c>
       <c r="E170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
+          <t>REAL summed Ookla test count backing ookla_dl_mbps/ookla_rtt_ms for the cell.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>target_is_degraded_next_1h</t>
+          <t>has_real_ookla_label</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
+          <t>True if ookla_dl_mbps is non-null — i.e. this row has a REAL label usable for training in cell_static_qoe_baseline.parquet.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>target_degradation_class_next_1h</t>
+          <t>qoe_risk_label</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>99.40000000000001</v>
+        <v>57.78</v>
       </c>
       <c r="E172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>3-class version of the next-hour forecast target.</t>
+          <t>high_risk/moderate_risk/low_risk from REAL ookla_dl_mbps thresholds. None where has_real_ookla_label is False (deliberately not guessed).</t>
         </is>
       </c>
     </row>
@@ -5946,16 +5946,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>target_qoe_index_next_1h</t>
+          <t>row_id</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
@@ -5966,7 +5966,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Continuous version of the next-hour forecast target.</t>
+          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
         </is>
       </c>
     </row>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>target_next_1h_valid</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -5998,7 +5998,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -6010,25 +6010,313 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>qoe_confidence_score</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>datetime64[us]</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>100</v>
       </c>
       <c r="E175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
+        <is>
+          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>target_qoe_index</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>100</v>
+      </c>
+      <c r="E176" t="b">
+        <v>0</v>
+      </c>
+      <c r="F176" t="b">
+        <v>0</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>target_service_quality_1to5</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>100</v>
+      </c>
+      <c r="E177" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" t="b">
+        <v>0</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>target_is_degraded</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>100</v>
+      </c>
+      <c r="E178" t="b">
+        <v>0</v>
+      </c>
+      <c r="F178" t="b">
+        <v>0</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>target_degradation_class</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>100</v>
+      </c>
+      <c r="E179" t="b">
+        <v>0</v>
+      </c>
+      <c r="F179" t="b">
+        <v>0</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>target_is_degraded_next_1h</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E180" t="b">
+        <v>0</v>
+      </c>
+      <c r="F180" t="b">
+        <v>0</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>target_degradation_class_next_1h</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E181" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" t="b">
+        <v>0</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>3-class version of the next-hour forecast target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>target_qoe_index_next_1h</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E182" t="b">
+        <v>0</v>
+      </c>
+      <c r="F182" t="b">
+        <v>0</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Continuous version of the next-hour forecast target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>target_next_1h_valid</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>100</v>
+      </c>
+      <c r="E183" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" t="b">
+        <v>0</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>qoe_confidence_score</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>100</v>
+      </c>
+      <c r="E184" t="b">
+        <v>1</v>
+      </c>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
         <is>
           <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
         </is>

--- a/data/outputs/feature_dictionary.xlsx
+++ b/data/outputs/feature_dictionary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,15 +1019,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57.78</v>
+        <v>59.98</v>
       </c>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Only non-null when qoe_level_is_ookla_anchored is True — a direct proxy for anchor status, same exclusion reason.</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>REAL Ookla quarterly test count for this cell (constant across all 168 simulated hours by definition — it is a QUARTERLY total, never a per-hour figure). NaN if the cell has no Ookla tile coverage.</t>
@@ -1051,15 +1055,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>57.78</v>
+        <v>59.98</v>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Only non-null when qoe_level_is_ookla_anchored is True — a direct proxy for anchor status, same exclusion reason.</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>REAL Ookla quarterly unique-device count for this cell (constant across all 168 simulated hours; quarterly, not hourly). NaN if unavailable in the source tile or no coverage exists.</t>
@@ -1086,12 +1094,16 @@
         <v>100</v>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Human-readable restatement of qoe_level_is_ookla_anchored — same exclusion reason.</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Human-readable provenance string: 'ookla_q4_2024_static_anchor' or 'no_real_anchor_simulated_only'. Complements the qoe_level_is_ookla_anchored boolean.</t>
@@ -1118,12 +1130,16 @@
         <v>100</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Near-perfectly determines whether target_is_degraded_next_1h can be positive at all on the simulated panel — see run_full_validation's validate_target_anchor_correlation warning for the current split. Excluded from the default feature list, not just flagged.</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>True if a real Ookla quarterly average existed to re-centre this cell's simulated hourly values on (~41% of cells). False does not mean 'less real' shape — the hourly SHAPE is simulated either way.</t>
@@ -1970,27 +1986,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>h3_parent_res6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>100</v>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+          <t>Coarse H3 resolution-6 parent of h3_index (~130 groups over the current grid). Use for SPATIAL HOLDOUT splits — hold out whole groups, don't randomly sample individual h3_index values (spatially autocorrelated neighbours would leak across a random split). Structural/grouping key, not an ML feature.</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2018,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>opencellid_record_count</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2022,7 +2038,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2050,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2054,7 +2070,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2082,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2086,7 +2102,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2114,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2118,7 +2134,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2146,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>tower_source</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2150,7 +2166,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2162,27 +2178,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>100</v>
       </c>
       <c r="E55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2210,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2214,7 +2230,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Real summed footprint area (m^2) per cell.</t>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2242,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2246,7 +2262,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2274,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2278,7 +2294,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>building_count / real cell area (km^2).</t>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2306,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2310,7 +2326,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>total_building_area_m2 / building_count.</t>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2338,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2342,7 +2358,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2370,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2374,7 +2390,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2402,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2406,7 +2422,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2434,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2438,7 +2454,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2466,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2470,7 +2486,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Real OSM POI count: tagged office=*.</t>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2498,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2502,7 +2518,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2530,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2534,7 +2550,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2562,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2566,7 +2582,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>road_length_m / 1000 / real cell area (km^2).</t>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2594,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2598,7 +2614,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Real OSM road-network node count per cell.</t>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2626,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2630,7 +2646,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>intersection_count / real cell area (km^2).</t>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2658,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2662,7 +2678,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2690,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2694,7 +2710,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2722,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2726,7 +2742,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2758,7 +2774,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2786,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2790,7 +2806,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>population_night / real cell area (km^2, projected CRS).</t>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2818,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2822,7 +2838,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2850,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2854,7 +2870,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
@@ -2866,12 +2882,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>demand_pressure_base</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2886,7 +2902,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2914,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>demand_pressure_index_pre_spatial</t>
+          <t>demand_pressure_base</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2915,14 +2931,10 @@
       <c r="F78" t="b">
         <v>1</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>demand_pressure_base plus a historical-QoE component. Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
+          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2946,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>spatial_lag_dl_median</t>
+          <t>demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2946,15 +2958,19 @@
         <v>100</v>
       </c>
       <c r="E79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp (real libpysal weights).</t>
+          <t>demand_pressure_base plus a historical-QoE component. Same circularity as demand_pressure_index, pre-spatial-smoothing.</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2982,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>spatial_var_dl_median</t>
+          <t>spatial_lag_dl_median</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2978,7 +2994,7 @@
         <v>100</v>
       </c>
       <c r="E80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -2986,7 +3002,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of dl_median at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor average of dl_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3014,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>spatial_lag_rtt_median</t>
+          <t>spatial_var_dl_median</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3010,7 +3026,7 @@
         <v>100</v>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -3018,7 +3034,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor variance of dl_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>spatial_var_rtt_median</t>
+          <t>spatial_lag_rtt_median</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3042,7 +3058,7 @@
         <v>100</v>
       </c>
       <c r="E82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -3050,7 +3066,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of rtt_median at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor average of rtt_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3078,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>spatial_lag_population_night</t>
+          <t>spatial_var_rtt_median</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3082,7 +3098,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor variance of rtt_median at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3110,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>spatial_var_population_night</t>
+          <t>spatial_lag_population_night</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3114,7 +3130,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of population_night at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor average of population_night at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3142,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
+          <t>spatial_var_population_night</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3146,7 +3162,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor variance of population_night at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3174,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>spatial_var_demand_pressure_index_pre_spatial</t>
+          <t>spatial_lag_demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3178,7 +3194,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Row-standardized H3 1-ring neighbor variance of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
+          <t>Row-standardized H3 1-ring neighbor average of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3206,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>demand_pressure_index</t>
+          <t>spatial_var_demand_pressure_index_pre_spatial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3207,14 +3223,10 @@
       <c r="F87" t="b">
         <v>1</v>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Final spatially-smoothed demand pressure index. Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
+          <t>Row-standardized H3 1-ring neighbor variance of demand_pressure_index_pre_spatial at the same timestamp (real libpysal weights).</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3238,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>spatial_rolling_mean_24h_dl_median</t>
+          <t>demand_pressure_index</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3243,10 +3255,14 @@
       <c r="F88" t="b">
         <v>1</v>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Final spatially-smoothed demand pressure index. Circular with the simulated QoE generator via its historical_qoe component (lag_24h_rtt_median). Use demand_pressure_base instead for a non-circular, real-data-only feature.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3274,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>gi_star_zscore_rtt_median</t>
+          <t>spatial_rolling_mean_24h_dl_median</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3278,7 +3294,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Real Getis-Ord Gi* z-score for latency (esda.G_Local, star=True) — the full Gi* expectation/variance formulation, not a plain standardized neighbor average.</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3306,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>gi_star_pvalue_rtt_median</t>
+          <t>gi_star_zscore_rtt_median</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>float32</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3310,7 +3326,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Permutation-based p-value (99 permutations) for the Getis-Ord Gi* statistic on rtt_median.</t>
+          <t>Real Getis-Ord Gi* z-score for latency (esda.G_Local, star=True) — the full Gi* expectation/variance formulation, not a plain standardized neighbor average.</t>
         </is>
       </c>
     </row>
@@ -3322,27 +3338,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hotspot_category_rtt_median</t>
+          <t>gi_star_pvalue_rtt_median</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float32</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>100</v>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Hot/cold spot classification at 90/95/99% confidence, from real esda.G_Local p-values.</t>
+          <t>Permutation-based p-value (99 permutations) for the Getis-Ord Gi* statistic on rtt_median.</t>
         </is>
       </c>
     </row>
@@ -3354,27 +3370,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>local_moran_i_rtt_median</t>
+          <t>hotspot_category_rtt_median</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>100</v>
       </c>
       <c r="E92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Local Moran's I statistic value for rtt_median (real esda.Moran_Local).</t>
+          <t>Hot/cold spot classification at 90/95/99% confidence, from real esda.G_Local p-values.</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3402,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>local_moran_pvalue_rtt_median</t>
+          <t>local_moran_i_rtt_median</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3406,7 +3422,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Permutation-based p-value (99 permutations) for Local Moran's I on rtt_median.</t>
+          <t>Local Moran's I statistic value for rtt_median (real esda.Moran_Local).</t>
         </is>
       </c>
     </row>
@@ -3418,27 +3434,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>local_moran_quadrant_rtt_median</t>
+          <t>local_moran_pvalue_rtt_median</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>100</v>
       </c>
       <c r="E94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>HH/LH/LL/HL spatial cluster/outlier classification (real esda.Moran_Local).</t>
+          <t>Permutation-based p-value (99 permutations) for Local Moran's I on rtt_median.</t>
         </is>
       </c>
     </row>
@@ -3450,27 +3466,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>historical_hotspot_freq_rtt_median</t>
+          <t>local_moran_quadrant_rtt_median</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>100</v>
       </c>
       <c r="E95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real (esda-confirmed) hotspot.</t>
+          <t>HH/LH/LL/HL spatial cluster/outlier classification (real esda.Moran_Local).</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3498,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>hotspot_category_rtt_median_encoded</t>
+          <t>historical_hotspot_freq_rtt_median</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3502,7 +3518,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ordinal-encoded hotspot confidence band (0=cold_99, 1=cold_95, 2=cold_90, 3=not_significant, 4=hot_90, 5=hot_95, 6=hot_99). ML-compatible integer version of hotspot_category_rtt_median (string, kept for dashboard).</t>
+          <t>Rolling (shift(1)-based, leakage-free) fraction of past hours this cell was a real (esda-confirmed) hotspot.</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3530,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>local_moran_quadrant_rtt_median_encoded</t>
+          <t>hotspot_category_rtt_median_encoded</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3534,7 +3550,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Ordinal-encoded Local Moran's I spatial cluster/outlier class (0=not_significant, 1=LL, 2=LH, 3=HL, 4=HH). ML-compatible integer version of local_moran_quadrant_rtt_median (string, kept for dashboard).</t>
+          <t>Ordinal-encoded hotspot confidence band (0=cold_99, 1=cold_95, 2=cold_90, 3=not_significant, 4=hot_90, 5=hot_95, 6=hot_99). ML-compatible integer version of hotspot_category_rtt_median (string, kept for dashboard).</t>
         </is>
       </c>
     </row>
@@ -3546,27 +3562,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>target_qoe_index</t>
+          <t>local_moran_quadrant_rtt_median_encoded</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>100</v>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
+          <t>Ordinal-encoded Local Moran's I spatial cluster/outlier class (0=not_significant, 1=LL, 2=LH, 3=HL, 4=HH). ML-compatible integer version of local_moran_quadrant_rtt_median (string, kept for dashboard).</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3594,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>target_service_quality_1to5</t>
+          <t>target_qoe_index</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3598,7 +3614,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
+          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3626,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>target_service_quality_1to5</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3630,7 +3646,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
+          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3658,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>target_is_degraded</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3662,7 +3678,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
+          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
         </is>
       </c>
     </row>
@@ -3674,27 +3690,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>qoe_confidence_score</t>
+          <t>target_degradation_class</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>100</v>
       </c>
       <c r="E102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
+          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3722,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>target_is_degraded_next_1h</t>
+          <t>qoe_confidence_score</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3715,18 +3731,18 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
+          <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3754,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>target_degradation_class_next_1h</t>
+          <t>target_is_degraded_next_1h</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3758,7 +3774,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>3-class version of the next-hour forecast target.</t>
+          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3786,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>target_qoe_index_next_1h</t>
+          <t>target_degradation_class_next_1h</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3790,7 +3806,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Continuous version of the next-hour forecast target.</t>
+          <t>3-class version of the next-hour forecast target.</t>
         </is>
       </c>
     </row>
@@ -3802,16 +3818,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>target_next_1h_valid</t>
+          <t>target_qoe_index_next_1h</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
@@ -3822,7 +3838,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+          <t>Continuous version of the next-hour forecast target.</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3850,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>priority_exposure_score</t>
+          <t>target_next_1h_valid</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3854,7 +3870,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>MinMax-scaled population_day floored at 0.01 — the population-exposure component of the Priority Score. Not an ML feature (derived from population_day).</t>
+          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3882,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>priority_base_score</t>
+          <t>priority_exposure_score</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3886,39 +3902,39 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>priority_exposure_score × historical_hotspot_freq × max(0.1, qoe_confidence_score) — pre-computed Priority Score base without model risk probability. Dashboard: final_priority = model_predicted_risk × priority_base_score. Not an ML feature.</t>
+          <t>MinMax-scaled population_day floored at 0.01 — the population-exposure component of the Priority Score. Not an ML feature (derived from population_day).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>cell_static_features</t>
+          <t>cell_time_dataset</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>priority_base_score</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>100</v>
       </c>
       <c r="E109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+          <t>priority_exposure_score × historical_hotspot_freq × max(0.1, qoe_confidence_score) — pre-computed Priority Score base without model risk probability. Dashboard: final_priority = model_predicted_risk × priority_base_score. Not an ML feature.</t>
         </is>
       </c>
     </row>
@@ -3930,27 +3946,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>100</v>
       </c>
       <c r="E110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -3962,27 +3978,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>opencellid_record_count</t>
+          <t>h3_parent_res6</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>100</v>
       </c>
       <c r="E111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+          <t>Coarse H3 resolution-6 parent of h3_index (~130 groups over the current grid). Use for SPATIAL HOLDOUT splits — hold out whole groups, don't randomly sample individual h3_index values (spatially autocorrelated neighbours would leak across a random split). Structural/grouping key, not an ML feature.</t>
         </is>
       </c>
     </row>
@@ -3994,12 +4010,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4014,7 +4030,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4042,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4046,7 +4062,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4074,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4078,7 +4094,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4106,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>tower_source</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4110,7 +4126,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4138,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4142,7 +4158,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -4154,27 +4170,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>100</v>
       </c>
       <c r="E117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Real summed footprint area (m^2) per cell.</t>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4202,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4206,7 +4222,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4234,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4238,7 +4254,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>building_count / real cell area (km^2).</t>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4266,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4270,7 +4286,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>total_building_area_m2 / building_count.</t>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4298,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4302,7 +4318,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4330,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4334,7 +4350,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4362,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4366,7 +4382,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4394,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4398,7 +4414,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4426,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4430,7 +4446,7 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Real OSM POI count: tagged office=*.</t>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4458,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4462,7 +4478,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4490,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4494,7 +4510,7 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -4506,12 +4522,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4526,7 +4542,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>road_length_m / 1000 / real cell area (km^2).</t>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4554,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4558,7 +4574,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Real OSM road-network node count per cell.</t>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4590,7 +4606,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>intersection_count / real cell area (km^2).</t>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4618,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4622,7 +4638,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4650,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -4654,7 +4670,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4682,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -4686,7 +4702,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4714,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -4718,7 +4734,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4746,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -4750,7 +4766,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>population_night / real cell area (km^2, projected CRS).</t>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4778,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4782,7 +4798,7 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
@@ -4794,12 +4810,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -4814,7 +4830,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4842,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>demand_pressure_base</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4846,24 +4862,24 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -4878,24 +4894,24 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>cell_static_qoe_baseline</t>
+          <t>cell_static_features</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>tower_count</t>
+          <t>demand_pressure_base</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -4910,7 +4926,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
+          <t>0-100 composite of ONLY real static features (population, POI, built-up, roads/transport). Zero QoE dependency — safe to use with any target, any mode.</t>
         </is>
       </c>
     </row>
@@ -4922,27 +4938,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>opencellid_record_count</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>100</v>
       </c>
       <c r="E141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -4954,27 +4970,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>tower_density_per_km2</t>
+          <t>h3_parent_res6</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>100</v>
       </c>
       <c r="E142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
+          <t>Coarse H3 resolution-6 parent of h3_index (~130 groups over the current grid). Use for SPATIAL HOLDOUT splits — hold out whole groups, don't randomly sample individual h3_index values (spatially autocorrelated neighbours would leak across a random split). Structural/grouping key, not an ML feature.</t>
         </is>
       </c>
     </row>
@@ -4986,12 +5002,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>dist_to_nearest_tower_m</t>
+          <t>tower_count</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5006,7 +5022,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
+          <t>Deduplicated approximate PHYSICAL SITE count (OpenCellID records collapsed by ~11m coordinate rounding) — see opencellid_record_count for the raw, non-deduplicated record count.</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5034,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>tower_is_synthetic</t>
+          <t>opencellid_record_count</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5038,7 +5054,7 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>True if tower used a synthetic fallback (raw source file missing).</t>
+          <t>Raw OpenCellID record count per cell BEFORE deduplication — includes multiple sectors/technologies/operators at the same physical site. Use tower_count for a physical-site estimate.</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5066,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>tower_source</t>
+          <t>tower_density_per_km2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5070,7 +5086,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
+          <t>Undocumented — flag for the Data/GIS lead rather than guessing; do not assume this column is safe to use as-is.</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5098,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>building_count</t>
+          <t>dist_to_nearest_tower_m</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5102,7 +5118,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
+          <t>Real geometric nearest-neighbor distance (sjoin_nearest, projected CRS) from the cell centroid to the nearest deduplicated OpenCellID site.</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5130,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>total_building_area_m2</t>
+          <t>tower_is_synthetic</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5134,7 +5150,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Real summed footprint area (m^2) per cell.</t>
+          <t>True if tower used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -5146,27 +5162,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>built_up_ratio</t>
+          <t>tower_source</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D148" t="n">
         <v>100</v>
       </c>
       <c r="E148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
+          <t>Provenance string: 'opencellid_deduplicated' (real) or 'synthetic_fallback_no_file'.</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5194,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>building_density_per_km2</t>
+          <t>building_count</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5198,7 +5214,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>building_count / real cell area (km^2).</t>
+          <t>Real Google Open Buildings V3 footprint count per cell (confidence &gt;= 0.65 only).</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5226,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>avg_building_footprint_m2</t>
+          <t>total_building_area_m2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5230,7 +5246,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>total_building_area_m2 / building_count.</t>
+          <t>Real summed footprint area (m^2) per cell.</t>
         </is>
       </c>
     </row>
@@ -5242,12 +5258,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>building_is_synthetic</t>
+          <t>built_up_ratio</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5262,7 +5278,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>True if building used a synthetic fallback (raw source file missing).</t>
+          <t>Real building footprint area / real H3 cell area (both from GIS geometry, not a hardcoded constant).</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5290,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>poi_education_count</t>
+          <t>building_density_per_km2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5294,7 +5310,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
+          <t>building_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -5306,12 +5322,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>poi_healthcare_count</t>
+          <t>avg_building_footprint_m2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5326,7 +5342,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
+          <t>total_building_area_m2 / building_count.</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5354,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>poi_retail_food_count</t>
+          <t>building_is_synthetic</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5358,7 +5374,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
+          <t>True if building used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5386,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>poi_office_count</t>
+          <t>poi_education_count</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5390,7 +5406,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Real OSM POI count: tagged office=*.</t>
+          <t>Real OSM POI count: schools, universities, colleges, kindergartens.</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5418,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>poi_recreation_count</t>
+          <t>poi_healthcare_count</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5422,7 +5438,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Real OSM POI count: leisure=* or tourism=*.</t>
+          <t>Real OSM POI count: hospitals, clinics, pharmacies, doctors.</t>
         </is>
       </c>
     </row>
@@ -5434,12 +5450,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>road_length_m</t>
+          <t>poi_retail_food_count</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5454,7 +5470,7 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
+          <t>Real OSM POI count: restaurants, cafes, fast food, shops.</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5482,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>road_density_km_per_km2</t>
+          <t>poi_office_count</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5486,7 +5502,7 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>road_length_m / 1000 / real cell area (km^2).</t>
+          <t>Real OSM POI count: tagged office=*.</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5514,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>intersection_count</t>
+          <t>poi_recreation_count</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5518,7 +5534,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Real OSM road-network node count per cell.</t>
+          <t>Real OSM POI count: leisure=* or tourism=*.</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5546,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>intersection_density_per_km2</t>
+          <t>road_length_m</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5550,7 +5566,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>intersection_count / real cell area (km^2).</t>
+          <t>Real road length (m) per cell via polygon overlay in a projected CRS (not a heuristic).</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5578,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>dist_to_nearest_transit_m</t>
+          <t>road_density_km_per_km2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5582,7 +5598,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
+          <t>road_length_m / 1000 / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5610,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>poi_transport_stop_count</t>
+          <t>intersection_count</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5614,7 +5630,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
+          <t>Real OSM road-network node count per cell.</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5642,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>osm_is_synthetic</t>
+          <t>intersection_density_per_km2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -5646,7 +5662,7 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>True if osm used a synthetic fallback (raw source file missing).</t>
+          <t>intersection_count / real cell area (km^2).</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5674,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>population_night</t>
+          <t>dist_to_nearest_transit_m</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5678,7 +5694,7 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
+          <t>Real geometric nearest-neighbor distance to the nearest OSM transit/rail POI (sjoin_nearest, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5706,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>population_density_per_km2</t>
+          <t>poi_transport_stop_count</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -5710,7 +5726,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>population_night / real cell area (km^2, projected CRS).</t>
+          <t>Real OSM POI count of public-transport/rail stops joined into the cell.</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5738,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>population_day</t>
+          <t>osm_is_synthetic</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -5742,7 +5758,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
+          <t>True if osm used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5770,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>population_is_synthetic</t>
+          <t>population_night</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -5774,7 +5790,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>True if population used a synthetic fallback (raw source file missing).</t>
+          <t>Real WorldPop 2020 zonal-statistics residential population estimate for the cell.</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5802,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ookla_dl_mbps</t>
+          <t>population_density_per_km2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5795,7 +5811,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E168" t="b">
         <v>1</v>
@@ -5806,7 +5822,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>REAL Ookla tests-weighted mean download speed (Mbps) for the cell, static/quarterly. NaN where no tile coverage exists (not imputed).</t>
+          <t>population_night / real cell area (km^2, projected CRS).</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5834,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ookla_rtt_ms</t>
+          <t>population_day</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5827,7 +5843,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E169" t="b">
         <v>1</v>
@@ -5838,7 +5854,7 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>REAL Ookla tests-weighted mean latency (ms) for the cell, static/quarterly. NaN where no tile coverage exists.</t>
+          <t>Modelled daytime population (residential population reweighted by real OSM office/retail density) — explicitly an assumption, not a raster.</t>
         </is>
       </c>
     </row>
@@ -5850,16 +5866,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ookla_tests</t>
+          <t>population_is_synthetic</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>57.78</v>
+        <v>100</v>
       </c>
       <c r="E170" t="b">
         <v>1</v>
@@ -5870,7 +5886,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>REAL summed Ookla test count backing ookla_dl_mbps/ookla_rtt_ms for the cell.</t>
+          <t>True if population used a synthetic fallback (raw source file missing).</t>
         </is>
       </c>
     </row>
@@ -5882,27 +5898,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>has_real_ookla_label</t>
+          <t>ookla_dl_mbps</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>100</v>
+        <v>59.98</v>
       </c>
       <c r="E171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" t="b">
-        <v>1</v>
-      </c>
-      <c r="G171" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>This IS the Option A modelling target — never a feature.</t>
+        </is>
+      </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>True if ookla_dl_mbps is non-null — i.e. this row has a REAL label usable for training in cell_static_qoe_baseline.parquet.</t>
+          <t>REAL Ookla tests-weighted mean download speed (Mbps) for the cell, static/quarterly. NaN where no tile coverage exists (not imputed).</t>
         </is>
       </c>
     </row>
@@ -5914,48 +5934,52 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>qoe_risk_label</t>
+          <t>ookla_rtt_ms</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>57.78</v>
+        <v>59.98</v>
       </c>
       <c r="E172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" t="b">
-        <v>1</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>This IS the Option A modelling target — never a feature.</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>high_risk/moderate_risk/low_risk from REAL ookla_dl_mbps thresholds. None where has_real_ookla_label is False (deliberately not guessed).</t>
+          <t>REAL Ookla tests-weighted mean latency (ms) for the cell, static/quarterly. NaN where no tile coverage exists.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>row_id</t>
+          <t>ookla_tests</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>100</v>
+        <v>59.98</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
@@ -5963,27 +5987,31 @@
       <c r="F173" t="b">
         <v>0</v>
       </c>
-      <c r="G173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Real quarterly Ookla sample count — target-adjacent, never a feature.</t>
+        </is>
+      </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
+          <t>REAL summed Ookla test count backing ookla_dl_mbps/ookla_rtt_ms for the cell.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>h3_index</t>
+          <t>has_real_ookla_label</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -5995,31 +6023,35 @@
       <c r="F174" t="b">
         <v>0</v>
       </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Split indicator (labelled vs. prediction-target cells), not a predictor — training on it would leak which rows have a real label.</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Uber H3 res-8 cell identifier (join key).</t>
+          <t>True if ookla_dl_mbps is non-null — i.e. this row has a REAL label usable for training in cell_static_qoe_baseline.parquet.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>qoe_targets</t>
+          <t>cell_static_qoe_baseline</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>qoe_risk_label</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>100</v>
+        <v>59.98</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
@@ -6027,10 +6059,14 @@
       <c r="F175" t="b">
         <v>0</v>
       </c>
-      <c r="G175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Directly thresholded from ookla_dl_mbps (the target) — using it as a feature reads the answer off a relabelled copy of itself.</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
+          <t>high_risk/moderate_risk/low_risk from REAL ookla_dl_mbps thresholds. None where has_real_ookla_label is False (deliberately not guessed).</t>
         </is>
       </c>
     </row>
@@ -6042,12 +6078,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>target_qoe_index</t>
+          <t>row_id</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6062,7 +6098,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
+          <t>Surrogate unique row identifier (h3_index + timestamp composite, as int).</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6110,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>target_service_quality_1to5</t>
+          <t>h3_index</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6094,7 +6130,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
+          <t>Uber H3 res-8 cell identifier (join key).</t>
         </is>
       </c>
     </row>
@@ -6106,12 +6142,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>target_is_degraded</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>datetime64[us]</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6126,7 +6162,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
+          <t>Hourly timestamp (UTC-naive, local Klang Valley convention).</t>
         </is>
       </c>
     </row>
@@ -6138,12 +6174,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>target_degradation_class</t>
+          <t>target_qoe_index</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6158,7 +6194,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
+          <t>Custom composite 0-100 QoE index (log-utility download/upload minus exponential latency/loss penalty). NOT a validated ITU-T G.107 MOS — see qoe_target.py docstring.</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6206,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>target_is_degraded_next_1h</t>
+          <t>target_service_quality_1to5</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6179,7 +6215,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
@@ -6190,7 +6226,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
+          <t>1-5 linear rescaling of target_qoe_index. NOT a validated MOS/ACR score.</t>
         </is>
       </c>
     </row>
@@ -6202,16 +6238,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>target_degradation_class_next_1h</t>
+          <t>target_is_degraded</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
@@ -6222,7 +6258,7 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>3-class version of the next-hour forecast target.</t>
+          <t>Binary SAME-HOUR degradation flag, derived from target_degradation_class &gt;= 1 (single shared threshold source — config.QOE_THRESHOLDS — so this can no longer disagree with target_degradation_class).</t>
         </is>
       </c>
     </row>
@@ -6234,16 +6270,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>target_qoe_index_next_1h</t>
+          <t>target_degradation_class</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
@@ -6254,7 +6290,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Continuous version of the next-hour forecast target.</t>
+          <t>0=normal, 1=degraded, 2=severe. Same threshold source as target_is_degraded.</t>
         </is>
       </c>
     </row>
@@ -6266,16 +6302,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>target_next_1h_valid</t>
+          <t>target_is_degraded_next_1h</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
@@ -6286,7 +6322,7 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+          <t>RECOMMENDED PRIMARY ML TARGET. target_is_degraded shifted -1 per cell (groupby h3_index).shift(-1) — genuinely predicting the future, not classifying the present. NaN/0-valid for each cell's final row (no future observation exists).</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6334,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>qoe_confidence_score</t>
+          <t>target_degradation_class_next_1h</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6307,18 +6343,186 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
+          <t>3-class version of the next-hour forecast target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>target_qoe_index_next_1h</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E185" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" t="b">
+        <v>0</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Continuous version of the next-hour forecast target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>target_next_1h_valid</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>100</v>
+      </c>
+      <c r="E186" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" t="b">
+        <v>0</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1 if a real future observation existed to build the next-hour target from; 0 for each cell's final row. Drop rows where this is 0 before training — do not treat them as a 'not degraded' case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>qoe_confidence_score</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>100</v>
+      </c>
+      <c r="E187" t="b">
+        <v>1</v>
+      </c>
+      <c r="F187" t="b">
+        <v>1</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
           <t>min(1.0, test_sample_count / 10) — higher sample count = more confidence in the cell-hour's QoE estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>qoe_level_is_ookla_anchored</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>100</v>
+      </c>
+      <c r="E188" t="b">
+        <v>0</v>
+      </c>
+      <c r="F188" t="b">
+        <v>0</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Near-perfectly determines whether target_is_degraded_next_1h can be positive at all on the simulated panel — see run_full_validation's validate_target_anchor_correlation warning for the current split. Excluded from the default feature list, not just flagged.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>True if a real Ookla quarterly average existed to re-centre this cell's simulated hourly values on (~41% of cells). False does not mean 'less real' shape — the hourly SHAPE is simulated either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>qoe_targets</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>qoe_baseline_source</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>100</v>
+      </c>
+      <c r="E189" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" t="b">
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Human-readable restatement of qoe_level_is_ookla_anchored — same exclusion reason.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Human-readable provenance string: 'ookla_q4_2024_static_anchor' or 'no_real_anchor_simulated_only'. Complements the qoe_level_is_ookla_anchored boolean.</t>
         </is>
       </c>
     </row>
